--- a/apps/api/assets/vocabulary/小学/人教版/五年级下.xlsx
+++ b/apps/api/assets/vocabulary/小学/人教版/五年级下.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D157"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -498,6 +498,16 @@
           <t>have ... class</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 上课；指上课；该上课了</t>
@@ -508,6 +518,16 @@
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>play sports</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -546,6 +566,16 @@
           <t>do morning exercises</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 做早操；晨练；做早操要说</t>
@@ -558,6 +588,16 @@
           <t>eat dinner</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 吃晚饭；吃晚餐；吃饭</t>
@@ -570,6 +610,16 @@
           <t>clean my room</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -582,6 +632,16 @@
           <t>go for a walk</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 出去散步
@@ -593,6 +653,16 @@
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>go shopping</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -653,6 +723,16 @@
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>take a dancing class</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1197,6 +1277,16 @@
           <t>go swimming</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 去游泳
@@ -1382,6 +1472,16 @@
           <t>go on a picnic</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 去野餐；去野炊；搞野餐</t>
@@ -1419,6 +1519,16 @@
           <t>pick apples</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 摘苹果；就像去摘苹果；采摘苹果</t>
@@ -1454,6 +1564,16 @@
           <t>make a snowman</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 堆雪人；做雪人；堆一个雪人</t>
@@ -1464,6 +1584,16 @@
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>go swimming</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1553,6 +1683,16 @@
           <t>good job</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 做得好；干得好；干的好</t>
@@ -2051,6 +2191,16 @@
           <t>a few</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 几个；〔反语〕很多；〈俚〉一点点
@@ -2112,6 +2262,16 @@
           <t>sports meet</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 运动会
@@ -2243,6 +2403,16 @@
           <t>the Great Wall</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 长城；万里长城；中国万里长城</t>
@@ -2278,6 +2448,16 @@
           <t>National Day</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 国庆日
@@ -2312,6 +2492,16 @@
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -2728,6 +2918,16 @@
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>twenty-third</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -3314,6 +3514,16 @@
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>each other</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -3380,6 +3590,16 @@
           <t>doing morning exercises</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -3392,6 +3612,16 @@
           <t>having ... class</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -3404,6 +3634,16 @@
           <t>eating lunch</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -3416,6 +3656,16 @@
           <t>reading a book</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -3426,6 +3676,16 @@
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>listening to music</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -3465,6 +3725,16 @@
           <t>keep to the right</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 靠右边走；走正路
@@ -3478,6 +3748,16 @@
           <t>keep your desk clean</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -3488,6 +3768,16 @@
       <c r="A142" s="2" t="inlineStr">
         <is>
           <t>talk quietly</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -3527,6 +3817,16 @@
           <t>take turns</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 替换
@@ -3702,6 +4002,16 @@
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>have a look</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
